--- a/UTCUTS/A1_Outputs/reference_freeze/A-O_AR_Projections.xlsx
+++ b/UTCUTS/A1_Outputs/reference_freeze/A-O_AR_Projections.xlsx
@@ -14191,7 +14191,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E024652-0DCC-40C7-A28B-4BEA6B8BA8C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5B341E4-2F4C-4A3C-82FC-3109BC056854}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
